--- a/basedatos_partidas/salida/descompuestos/07.04.01.010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.04.01.010.xlsx
@@ -584,10 +584,10 @@
         <v>0.28</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -610,10 +610,10 @@
         <v>0.26</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="13">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>44.46</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="16">
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>55.93</v>
+        <v>56.2</v>
       </c>
       <c r="H26" t="n">
         <v>0.5600000000000001</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>56.49</v>
+        <v>56.76</v>
       </c>
     </row>
   </sheetData>
